--- a/artfynd/A 6839-2026 artfynd.xlsx
+++ b/artfynd/A 6839-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74112426</v>
+        <v>74112436</v>
       </c>
       <c r="B2" t="n">
-        <v>97822</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>783</v>
+        <v>737</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Mörk kraterlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Gyalecta truncigena</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
+          <t>(Ach.) Hepp</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>719739.7317738358</v>
+        <v>719705</v>
       </c>
       <c r="R2" t="n">
-        <v>6391179.057925974</v>
+        <v>6391214</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,21 +743,11 @@
           <t>2018-09-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-10-27</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,6 +756,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>lundalm</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Ulmus minor</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Ulmus minor</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -790,12 +790,7 @@
         <v>74112437</v>
       </c>
       <c r="B3" t="n">
-        <v>79135</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>719681.1668241288</v>
+        <v>719681</v>
       </c>
       <c r="R3" t="n">
-        <v>6391247.276284938</v>
+        <v>6391247</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,19 +855,9 @@
           <t>2018-09-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,37 +899,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74112449</v>
+        <v>74112426</v>
       </c>
       <c r="B4" t="n">
-        <v>86195</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>239233</v>
+        <v>783</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ekvaxskivling</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hygrophorus cossus</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Sowerby) Fr.</t>
+          <t>(L.) Harz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>719622.9927834896</v>
+        <v>719740</v>
       </c>
       <c r="R4" t="n">
-        <v>6391338.061179804</v>
+        <v>6391179</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -987,19 +967,9 @@
           <t>2018-09-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,37 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>74112424</v>
+        <v>74112418</v>
       </c>
       <c r="B5" t="n">
-        <v>87986</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79837</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>245042</v>
+        <v>1026</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>719656.2366815753</v>
+        <v>719762</v>
       </c>
       <c r="R5" t="n">
-        <v>6391250.754594347</v>
+        <v>6391128</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1099,19 +1064,9 @@
           <t>2018-09-26</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,37 +1093,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>74112438</v>
+        <v>74112424</v>
       </c>
       <c r="B6" t="n">
-        <v>88052</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90665</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1601</v>
+        <v>245042</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mjölmusseron</t>
+          <t>Besk kastanjemusseron</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tricholoma ustaloides</t>
+          <t>Tricholoma batschii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Romagn.</t>
+          <t>Mort. Chr. &amp; Noordel.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1178,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>719641.2209592126</v>
+        <v>719656</v>
       </c>
       <c r="R6" t="n">
-        <v>6391249.939710778</v>
+        <v>6391251</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1211,19 +1161,9 @@
           <t>2018-09-26</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,133 +1187,6 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>74112436</v>
-      </c>
-      <c r="B7" t="n">
-        <v>79135</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>737</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Mörk kraterlav</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Gyalecta truncigena</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Ach.) Hepp</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Gännorområdet, Gtl</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>719705.0136114776</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6391214.214168462</v>
-      </c>
-      <c r="S7" t="n">
-        <v>25</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Vallstena</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2018-09-26</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2018-10-27</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>lundalm</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Ulmus minor</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Ulmus minor</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Mikael Hagström</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Mikael Hagström</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6839-2026 artfynd.xlsx
+++ b/artfynd/A 6839-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112436</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112437</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112426</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112418</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,8 +1212,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74112424</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>